--- a/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_MOVISTAR ESTUDIANTES.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_MOVISTAR ESTUDIANTES.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,7 +775,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. APARICIO RODRÍGUEZ</t>
+          <t>H. APARICIO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -784,70 +784,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3075</v>
+        <v>-0.1266000000000002</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3075</v>
+        <v>-0.2784000000000002</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.1519000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3075</v>
+        <v>2.618</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3075</v>
+        <v>-3.1595</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>5.7776</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3075</v>
+        <v>4.112900000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3075</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4.6657</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-1.4947</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-2.6066</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.1119</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-2.1448</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-5.069599999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.9248</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.0101</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.06829999999999997</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.05809999999999996</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.6101</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2201</v>
       </c>
     </row>
     <row r="6">
@@ -931,7 +931,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. APARICIO RODRIGUEZ</t>
+          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -940,76 +940,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4342000000000001</v>
+        <v>-1.8998</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5859000000000001</v>
+        <v>0.1345</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1519000000000001</v>
+        <v>-2.0343</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3105</v>
+        <v>-0.4337000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.467</v>
+        <v>-0.004600000000000104</v>
       </c>
       <c r="I7" t="n">
-        <v>5.7776</v>
+        <v>-0.4290000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8053</v>
+        <v>2.2727</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8604000000000001</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>4.6657</v>
+        <v>1.5795</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4947</v>
+        <v>-2.7064</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.6066</v>
+        <v>-0.6977</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1119</v>
+        <v>-2.0085</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.1448</v>
+        <v>0.9750999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.069599999999999</v>
+        <v>-1.1699</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9248</v>
+        <v>2.1449</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0101</v>
+        <v>-1.5524</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06829999999999997</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.05809999999999996</v>
+        <v>-0.5841999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6101</v>
+        <v>-0.8886000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>0.61</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2201</v>
+        <v>-0.8886000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
+          <t>G. PEREZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1021,73 +1021,73 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8998</v>
+        <v>-2.9166</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1345</v>
+        <v>-2.0832</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0343</v>
+        <v>-0.8333000000000002</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4337000000000001</v>
+        <v>-1.9973</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.004600000000000104</v>
+        <v>-1.029</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4290000000000001</v>
+        <v>-0.9681999999999997</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2727</v>
+        <v>0.5518</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6929999999999999</v>
+        <v>-0.3226999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5795</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.7064</v>
+        <v>-2.5492</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6977</v>
+        <v>-0.7062999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.0085</v>
+        <v>-1.8428</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9750999999999999</v>
+        <v>0.7799</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1699</v>
+        <v>-4.0947</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1449</v>
+        <v>4.8746</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5524</v>
+        <v>-1.6463</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-1.206</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5841999999999999</v>
+        <v>-0.4402</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8886000000000001</v>
+        <v>-0.05290000000000006</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.6658</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8886000000000001</v>
+        <v>-2.7187</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. PEREZ HERNANDEZ</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1099,73 +1099,73 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9166</v>
+        <v>-3.3379</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0832</v>
+        <v>-0.8023999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8333000000000002</v>
+        <v>-2.5356</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9973</v>
+        <v>-2.1011</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.029</v>
+        <v>-2.5535</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9681999999999997</v>
+        <v>0.4526000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5518</v>
+        <v>0.5957</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3226999999999999</v>
+        <v>-1.0323</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8745000000000001</v>
+        <v>1.628</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.5492</v>
+        <v>-2.6967</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7062999999999999</v>
+        <v>-1.5212</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.8428</v>
+        <v>-1.1755</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7799</v>
+        <v>1.5599</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.0947</v>
+        <v>-2.5349</v>
       </c>
       <c r="R9" t="n">
-        <v>4.8746</v>
+        <v>4.0946</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6463</v>
+        <v>0.8633</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.206</v>
+        <v>-0.2561</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4402</v>
+        <v>1.1194</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.05290000000000006</v>
+        <v>-3.6602</v>
       </c>
       <c r="W9" t="n">
-        <v>2.6658</v>
+        <v>1.3929</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.7187</v>
+        <v>-5.0531</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>S. GRADIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1177,73 +1177,73 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3379</v>
+        <v>-4.4592</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8023999999999999</v>
+        <v>-4.6973</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5356</v>
+        <v>0.2381999999999997</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1011</v>
+        <v>-5.800000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.5535</v>
+        <v>1.5634</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4526000000000001</v>
+        <v>-7.363300000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5957</v>
+        <v>-2.7095</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.0323</v>
+        <v>2.273</v>
       </c>
       <c r="L10" t="n">
-        <v>1.628</v>
+        <v>-4.9825</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.6967</v>
+        <v>-3.0905</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5212</v>
+        <v>-0.7098</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1755</v>
+        <v>-2.3807</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5599</v>
+        <v>-1.3649</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.5349</v>
+        <v>-7.0195</v>
       </c>
       <c r="R10" t="n">
-        <v>4.0946</v>
+        <v>5.6545</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8633</v>
+        <v>2.4271</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2561</v>
+        <v>1.2517</v>
       </c>
       <c r="U10" t="n">
-        <v>1.1194</v>
+        <v>1.1755</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.6602</v>
+        <v>0.2784999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3929</v>
+        <v>3.78</v>
       </c>
       <c r="X10" t="n">
-        <v>-5.0531</v>
+        <v>-3.5014</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. GRADIN</t>
+          <t>D. DAMIAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,73 +1255,73 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4592</v>
+        <v>-4.6906</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6973</v>
+        <v>-9.041</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2381999999999997</v>
+        <v>4.350300000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.800000000000001</v>
+        <v>-5.6174</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5634</v>
+        <v>-5.746</v>
       </c>
       <c r="I11" t="n">
-        <v>-7.363300000000001</v>
+        <v>0.1286</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.7095</v>
+        <v>-3.6006</v>
       </c>
       <c r="K11" t="n">
-        <v>2.273</v>
+        <v>-4.4831</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.9825</v>
+        <v>0.8825</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.0905</v>
+        <v>-2.0168</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7098</v>
+        <v>-1.2627</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.3807</v>
+        <v>-0.7539</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3649</v>
+        <v>-2.3399</v>
       </c>
       <c r="Q11" t="n">
-        <v>-7.0195</v>
+        <v>-8.9694</v>
       </c>
       <c r="R11" t="n">
-        <v>5.6545</v>
+        <v>6.6295</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4271</v>
+        <v>1.6482</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2517</v>
+        <v>0.7963</v>
       </c>
       <c r="U11" t="n">
-        <v>1.1755</v>
+        <v>0.8519000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2784999999999999</v>
+        <v>1.6184</v>
       </c>
       <c r="W11" t="n">
-        <v>3.78</v>
+        <v>2.7326</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.5014</v>
+        <v>-1.1143</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. DAMIAN</t>
+          <t>F. ESPINOSA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1330,76 +1330,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6906</v>
+        <v>-5.6321</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.041</v>
+        <v>-8.325200000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>4.350300000000001</v>
+        <v>2.6931</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.6174</v>
+        <v>-3.0792</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.746</v>
+        <v>-3.3919</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1286</v>
+        <v>0.3127</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.6006</v>
+        <v>-1.2989</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.4831</v>
+        <v>-0.2373999999999998</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8825</v>
+        <v>-1.0615</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.0168</v>
+        <v>-1.7803</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2627</v>
+        <v>-3.1545</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7539</v>
+        <v>1.3742</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.3399</v>
+        <v>-2.7298</v>
       </c>
       <c r="Q12" t="n">
-        <v>-8.9694</v>
+        <v>-6.2396</v>
       </c>
       <c r="R12" t="n">
-        <v>6.6295</v>
+        <v>3.5098</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6482</v>
+        <v>0.4554</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7963</v>
+        <v>-0.7339</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8519000000000001</v>
+        <v>1.1892</v>
       </c>
       <c r="V12" t="n">
-        <v>1.6184</v>
+        <v>-0.2786</v>
       </c>
       <c r="W12" t="n">
-        <v>2.7326</v>
+        <v>-0.0529</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1143</v>
+        <v>-0.2256</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. ESPINOSA</t>
+          <t>P. ROBLES LLANOS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1408,76 +1408,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.6321</v>
+        <v>-11.3626</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.325200000000001</v>
+        <v>-15.3385</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6931</v>
+        <v>3.9759</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.0792</v>
+        <v>-9.257999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.3919</v>
+        <v>-3.311</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3127</v>
+        <v>-5.947100000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.2989</v>
+        <v>-6.555499999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2373999999999998</v>
+        <v>-0.8181000000000003</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.0615</v>
+        <v>-5.737500000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7803</v>
+        <v>-2.7025</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.1545</v>
+        <v>-2.4929</v>
       </c>
       <c r="O13" t="n">
-        <v>1.3742</v>
+        <v>-0.2096</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.7298</v>
+        <v>-3.3148</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.2396</v>
+        <v>-11.5041</v>
       </c>
       <c r="R13" t="n">
-        <v>3.5098</v>
+        <v>8.189500000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4554</v>
+        <v>-0.4611999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7339</v>
+        <v>-1.3903</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1892</v>
+        <v>0.9291</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2786</v>
+        <v>1.6714</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.0529</v>
+        <v>4.111499999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2256</v>
+        <v>-2.4401</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. ROBLES LLANOS</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1489,144 +1489,66 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-11.3626</v>
+        <v>-22.0464</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.3385</v>
+        <v>-28.8502</v>
       </c>
       <c r="F14" t="n">
-        <v>3.9759</v>
+        <v>6.803700000000002</v>
       </c>
       <c r="G14" t="n">
-        <v>-9.257999999999999</v>
+        <v>-8.881900000000003</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.311</v>
+        <v>-17.745</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.947100000000001</v>
+        <v>8.863400000000004</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.555499999999999</v>
+        <v>19.81160000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.8181000000000003</v>
+        <v>0.6196999999999984</v>
       </c>
       <c r="L14" t="n">
-        <v>-5.737500000000001</v>
+        <v>19.19110000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.7025</v>
+        <v>-28.6932</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.4929</v>
+        <v>-18.3648</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2096</v>
+        <v>-10.3278</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.3148</v>
+        <v>-10.724</v>
       </c>
       <c r="Q14" t="n">
-        <v>-11.5041</v>
+        <v>-67.2701</v>
       </c>
       <c r="R14" t="n">
-        <v>8.189500000000001</v>
+        <v>56.5459</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4611999999999999</v>
+        <v>0.09130000000000005</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3903</v>
+        <v>-2.5728</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9291</v>
+        <v>2.6644</v>
       </c>
       <c r="V14" t="n">
-        <v>1.6714</v>
+        <v>-2.5321</v>
       </c>
       <c r="W14" t="n">
-        <v>4.111499999999999</v>
+        <v>21.1816</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.4401</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-22.0465</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-28.8502</v>
-      </c>
-      <c r="F15" t="n">
-        <v>6.803700000000002</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-8.8819</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-17.745</v>
-      </c>
-      <c r="I15" t="n">
-        <v>8.863400000000004</v>
-      </c>
-      <c r="J15" t="n">
-        <v>19.8115</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.6196999999999984</v>
-      </c>
-      <c r="L15" t="n">
-        <v>19.19110000000001</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-28.6932</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-18.3648</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-10.3278</v>
-      </c>
-      <c r="P15" t="n">
-        <v>-10.724</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-67.2701</v>
-      </c>
-      <c r="R15" t="n">
-        <v>56.5459</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.09130000000000005</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-2.5728</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.6644</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-2.5321</v>
-      </c>
-      <c r="W15" t="n">
-        <v>21.1816</v>
-      </c>
-      <c r="X15" t="n">
         <v>-23.7135</v>
       </c>
     </row>
